--- a/育児時短勤務手当金/育児時短勤務手当金請求書_電子申請書.xlsx
+++ b/育児時短勤務手当金/育児時短勤務手当金請求書_電子申請書.xlsx
@@ -2387,7 +2387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B19"/>
+  <dimension ref="B2:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" style="225" min="1" max="1"/>
@@ -2435,7 +2435,7 @@
     <row r="8">
       <c r="B8" s="229" t="inlineStr">
         <is>
-          <t>4. 「入力」シート最上段が緑色（✓）になったら、「請求書(表)」「請求書(裏)」を印刷し、所属機関の長の確認欄に記入・押印します。</t>
+          <t>4. 「入力」シート最上段が緑色（✓）になったら、「請求書(表)」「請求書(裏)」を印刷し、所属機関の長の確認欄に記入・押印します。（マクロ有効版は「入力」シート右上の［請求書を印刷］ボタンで表裏まとめて印刷）</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
     <row r="11">
       <c r="B11" s="229" t="inlineStr">
         <is>
-          <t>※1か月分ごとに1回請求します。翌月分は、このファイルを「名前を付けて保存」し、対象月と報酬額などを書き換えて使えます。</t>
+          <t>※1か月分ごとに1回請求します。翌月分は、このファイルを「名前を付けて保存」し、対象月と報酬額などを書き換えて使えます（マクロ有効版は［翌月分用にクリア］ボタンで月ごとに変わる項目だけ消せます）。</t>
         </is>
       </c>
     </row>
@@ -2473,36 +2473,67 @@
     <row r="14">
       <c r="B14" s="228" t="inlineStr">
         <is>
-          <t>■ 共済組合の方</t>
+          <t>■ マクロ有効版（.xlsm）のボタン　※ファイルを開いたとき「マクロを有効にする」を押してください</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="229" t="inlineStr">
         <is>
-          <t>・受け取ったファイルの「共済組合提出データ」シートの2行目をコピーし、管理台帳「請求記録」に値のみ貼り付けます。</t>
+          <t>［請求書を印刷］入力エラーがなければ「請求書(表)」「請求書(裏)」を続けて印刷。エラーがあるときは印刷せず、直す項目を一覧で表示します。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="229" t="inlineStr">
         <is>
+          <t>［翌月分用にクリア］対象月・報酬額・通勤手当（月額）・請求日・添付書類のチェックだけを消します（氏名・所属・子の情報などは残ります）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="229" t="inlineStr">
+        <is>
+          <t>※マクロ有効版は、請求書シートを［ファイル→印刷］で印刷した場合も、エラーが残っていれば印刷を止めます。マクロなし版（.xlsx）では、エラーが残ると請求書の下に赤字の警告が印字されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="227" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="228" t="inlineStr">
+        <is>
+          <t>■ 共済組合の方</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="229" t="inlineStr">
+        <is>
+          <t>・受け取ったファイルの「共済組合提出データ」シートの2行目をコピーし、管理台帳「請求記録」に値のみ貼り付けます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="229" t="inlineStr">
+        <is>
           <t>・請求期間の始期は『勤務開始日が月の途中ならその日から』で自動計算しています（運用が異なる場合はお知らせください）。</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="227" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="228" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="227" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="228" t="inlineStr">
         <is>
           <t>■ 動作環境</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="229" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="229" t="inlineStr">
         <is>
           <t>Excel 2013以降（マクロ不使用）。シートは保護（パスワードなし）されており、黄色いセル以外は書き換えできません。</t>
         </is>
@@ -2538,7 +2569,7 @@
     <col hidden="1" width="13" customWidth="1" style="225" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="32" customHeight="1" s="225">
       <c r="B1" s="230" t="inlineStr">
         <is>
           <t>育児時短勤務手当金請求書　入力シート</t>
